--- a/data/plan_pmp.xlsx
+++ b/data/plan_pmp.xlsx
@@ -1441,7 +1441,7 @@
     <t xml:space="preserve">Lien vers PDF </t>
   </si>
   <si>
-    <t>Mode_fonctionnement</t>
+    <t>mode_fonctionnement</t>
   </si>
 </sst>
 </file>
